--- a/artfynd/A 18853-2026 artfynd.xlsx
+++ b/artfynd/A 18853-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,6 +932,561 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133780840</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skrammelbäcken, Skrammelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>503733</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6639578</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133783902</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skrammelbäcken, Skrammelbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>503621</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6639467</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman, Per Arneborn, Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133779074</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skommar-Pelles äng, Skommar-Pelles äng, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>503940</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6639714</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133779504</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58641</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södra Ladbacken, Södra Ladbacken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>503877</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6639689</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133779366</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södra Ladbacken, Södra Ladbacken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>503910</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6639701</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18853-2026 artfynd.xlsx
+++ b/artfynd/A 18853-2026 artfynd.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Maria Berdén Evertsson</t>
+          <t>Lotta Sörman, Maria Berdén Evertsson, Per Arneborn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 18853-2026 artfynd.xlsx
+++ b/artfynd/A 18853-2026 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133779698</v>
+        <v>133780840</v>
       </c>
       <c r="B2" t="n">
-        <v>58117</v>
+        <v>5179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Ladbacken, Södra Ladbacken, Vstm</t>
+          <t>Skrammelbäcken, Skrammelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503864</v>
+        <v>503733</v>
       </c>
       <c r="R2" t="n">
-        <v>6639676</v>
+        <v>6639578</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,31 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133779586</v>
+        <v>133779698</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>58117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +813,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503866</v>
+        <v>503864</v>
       </c>
       <c r="R3" t="n">
-        <v>6639675</v>
+        <v>6639676</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska hack i död tall</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,26 +882,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133780840</v>
+        <v>133783902</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>58332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,34 +910,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skrammelbäcken, Skrammelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503733</v>
+        <v>503621</v>
       </c>
       <c r="R4" t="n">
-        <v>6639578</v>
+        <v>6639467</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1004,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1014,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,34 +1004,34 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Lotta Sörman, Per Arneborn, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133783902</v>
+        <v>133779074</v>
       </c>
       <c r="B5" t="n">
-        <v>58332</v>
+        <v>57955</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1072,19 +1042,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skrammelbäcken, Skrammelbäcken, Vstm</t>
+          <t>Skommar-Pelles äng, Skommar-Pelles äng, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503621</v>
+        <v>503940</v>
       </c>
       <c r="R5" t="n">
-        <v>6639467</v>
+        <v>6639714</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,14 +1116,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Maria Berdén Evertsson, Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133779074</v>
+        <v>133779586</v>
       </c>
       <c r="B6" t="n">
         <v>57955</v>
@@ -1189,17 +1159,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skommar-Pelles äng, Skommar-Pelles äng, Vstm</t>
+          <t>Södra Ladbacken, Södra Ladbacken, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503940</v>
+        <v>503866</v>
       </c>
       <c r="R6" t="n">
-        <v>6639714</v>
+        <v>6639675</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1208,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,16 +1224,41 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 18853-2026 artfynd.xlsx
+++ b/artfynd/A 18853-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133780840</v>
       </c>
       <c r="B2" t="n">
-        <v>5179</v>
+        <v>5181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133779698</v>
       </c>
       <c r="B3" t="n">
-        <v>58117</v>
+        <v>58124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133783902</v>
       </c>
       <c r="B4" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133779074</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>133779586</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>133779504</v>
       </c>
       <c r="B7" t="n">
-        <v>58641</v>
+        <v>58648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>133779366</v>
       </c>
       <c r="B8" t="n">
-        <v>58332</v>
+        <v>58339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 18853-2026 artfynd.xlsx
+++ b/artfynd/A 18853-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>133779698</v>
       </c>
       <c r="B3" t="n">
-        <v>58124</v>
+        <v>58134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133783902</v>
       </c>
       <c r="B4" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133779074</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>133779586</v>
       </c>
       <c r="B6" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>133779504</v>
       </c>
       <c r="B7" t="n">
-        <v>58648</v>
+        <v>58658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>133779366</v>
       </c>
       <c r="B8" t="n">
-        <v>58339</v>
+        <v>58349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 18853-2026 artfynd.xlsx
+++ b/artfynd/A 18853-2026 artfynd.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Maria Berdén Evertsson</t>
+          <t>Lotta Sörman, Maria Berdén Evertsson, Per Arneborn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 18853-2026 artfynd.xlsx
+++ b/artfynd/A 18853-2026 artfynd.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Maria Berdén Evertsson, Per Arneborn</t>
+          <t>Lotta Sörman, Per Arneborn, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 18853-2026 artfynd.xlsx
+++ b/artfynd/A 18853-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133780840</v>
+        <v>133779074</v>
       </c>
       <c r="B2" t="n">
-        <v>5181</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skrammelbäcken, Skrammelbäcken, Vstm</t>
+          <t>Skommar-Pelles äng, Skommar-Pelles äng, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503733</v>
+        <v>503940</v>
       </c>
       <c r="R2" t="n">
-        <v>6639578</v>
+        <v>6639714</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,27 +787,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133779698</v>
+        <v>133779586</v>
       </c>
       <c r="B3" t="n">
-        <v>58134</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -813,7 +818,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503864</v>
+        <v>503866</v>
       </c>
       <c r="R3" t="n">
-        <v>6639676</v>
+        <v>6639675</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,6 +892,26 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -899,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133783902</v>
+        <v>133780840</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>5181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skrammelbäcken, Skrammelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503621</v>
+        <v>503733</v>
       </c>
       <c r="R4" t="n">
-        <v>6639467</v>
+        <v>6639578</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,34 +1029,34 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lotta Sörman, Per Arneborn, Maria Berdén Evertsson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133779074</v>
+        <v>133779366</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,19 +1067,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skommar-Pelles äng, Skommar-Pelles äng, Vstm</t>
+          <t>Södra Ladbacken, Södra Ladbacken, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503940</v>
+        <v>503910</v>
       </c>
       <c r="R5" t="n">
-        <v>6639714</v>
+        <v>6639701</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,27 +1148,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133779586</v>
+        <v>133783902</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,22 +1179,22 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Ladbacken, Södra Ladbacken, Vstm</t>
+          <t>Skrammelbäcken, Skrammelbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503866</v>
+        <v>503621</v>
       </c>
       <c r="R6" t="n">
-        <v>6639675</v>
+        <v>6639467</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska hack i död tall</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,68 +1244,43 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman, Per Arneborn, Maria Berdén Evertsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133779504</v>
+        <v>133779698</v>
       </c>
       <c r="B7" t="n">
-        <v>58658</v>
+        <v>58134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>103020</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1305,13 +1300,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503877</v>
+        <v>503864</v>
       </c>
       <c r="R7" t="n">
-        <v>6639689</v>
+        <v>6639676</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,26 +1356,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133779366</v>
+        <v>133779504</v>
       </c>
       <c r="B8" t="n">
-        <v>58349</v>
+        <v>58658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1417,13 +1417,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>503910</v>
+        <v>503877</v>
       </c>
       <c r="R8" t="n">
-        <v>6639701</v>
+        <v>6639689</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 18853-2026 artfynd.xlsx
+++ b/artfynd/A 18853-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133779074</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133779586</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133780840</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1145,6 +1165,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133779366</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133783902</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133779698</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,8 +1521,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133779504</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>